--- a/docs/unit1/0_getting_started/(Starter-Workbook)-HW-A-Tour-of-Class-Resources.xlsx
+++ b/docs/unit1/0_getting_started/(Starter-Workbook)-HW-A-Tour-of-Class-Resources.xlsx
@@ -58,10 +58,10 @@
     <t>1. Take a screenshot of the Teaching Assistants page on our class website.</t>
   </si>
   <si>
-    <t>2. Take a picture of your OneDrive folder with your HW starter sheet in it. Make sure the screenshot shows the folder name you created in Part 1.</t>
-  </si>
-  <si>
-    <t>3. On our Class Website, navigate to the "Office Hours" tab and take a screenshot of the office hours for the first full week of the semester.</t>
+    <t>2. Take a picture of your class folder with your Homework starter sheet in it. Make sure the screenshot shows the folder name you created in Part 1.</t>
+  </si>
+  <si>
+    <t>3. On our class website, navigate to the "Office Hours" tab and take a screenshot of the office hours for September 14th to September 18th.</t>
   </si>
 </sst>
 </file>
